--- a/Tension_oferta_demanda_CdM.xlsx
+++ b/Tension_oferta_demanda_CdM.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodos + serie 5 años" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barrios (todos)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rentabilidad y esfuerzo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nodos + serie 5 años'!$A$4:$P$48</definedName>
@@ -21,12 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +69,31 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +125,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -125,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -143,6 +180,23 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6588,7 +6642,5418 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:J183"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Rentabilidad bruta del alquiler y esfuerzo de compra — CdM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Rentabilidad bruta = alquiler €/m²/mes × 12 ÷ venta €/m² (informe idealista: venta jun-2026, alquiler abr/jun-2026). Esfuerzo = años de renta neta íntegra del hogar medio (INE Atlas de Renta 2023) para pagar una vivienda de 80 m². Sin gastos, impuestos ni vacancia. Ordenado por rentabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Nodo</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Venta €/m²</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Alquiler €/m²/mes</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Δ alquiler anual</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Rentab. bruta</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Renta hogar 2023 €</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Esfuerzo (años, 80 m²)</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>Δ precio anual</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Población</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Puente de Vallecas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>3391</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>32666</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>253048</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Villanueva de la Cañada</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>3259</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>70766</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>24028</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Parla</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>2382</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>35177</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>137471</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Villaverde</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>3210</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>35011</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>167952</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Usera</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>3603</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>34651</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>149113</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Valdemoro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>2555</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>45042</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>85972</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Villaviciosa de Odón</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>3443</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>68382</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>30127</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Galapagar</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>2713</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>49504</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>36758</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Arganda del Rey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>2590</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>40353</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>60419</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Collado Villalba</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>2845</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>41413</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>67274</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Aranjuez</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>40453</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>63040</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Carabanchel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>3790</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>36350</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>274406</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Navalcarnero</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>2411</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>43431</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>33331</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>San Lorenzo de El Escorial</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>2833</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>44280</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>18872</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>3932</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>38078</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>250396</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2858</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>42700</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I20" s="20" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>56651</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Villa de Vallecas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>3829</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F21" s="22" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>39836</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>122337</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Torrelodones</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>2887</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>80733</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I22" s="20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>25433</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Alcalá de Henares</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>2903</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>41866</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>203208</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Torrejón de Ardoz</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>3078</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>41459</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I24" s="20" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>143526</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Coslada</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>3324</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>41836</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I25" s="20" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>80512</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>3277</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>41792</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I26" s="20" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>193238</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Móstoles</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>38622</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>214817</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>San Blas-Canillejas</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>4030</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>44468</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>166583</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>3258</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>38660</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>195734</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fuenlabrada</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>2856</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>38299</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>190076</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Paracuellos de Jarama</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>3063</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>63913</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>27650</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Arroyomolinos</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>2664</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>54546</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="J32" s="18" t="n">
+        <v>38075</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Vicálvaro</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>42870</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>89772</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Alcobendas</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>3983</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <v>65139</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" s="18" t="n">
+        <v>123342</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rivas-Vaciamadrid</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>3166</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>54628</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>103148</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Alcorcón</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>3388</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F36" s="22" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>41634</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J36" s="18" t="n">
+        <v>175719</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>San Sebastián de los Reyes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>4145</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>52413</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J37" s="18" t="n">
+        <v>96992</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>6013</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>49916</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J38" s="18" t="n">
+        <v>3506730</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Colmenar Viejo</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>3111</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>52003</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>58730</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ciudad Lineal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>5174</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>46937</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>230035</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tetuán</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>6147</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>45762</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>166211</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Rozas de Madrid, Las</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>4083</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>74371</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>99037</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Moratalaz</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>4607</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>42823</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J43" s="18" t="n">
+        <v>95123</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Arganzuela</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>6389</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>52857</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>156559</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>7636</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>44958</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="n">
+        <v>145411</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Moncloa-Aravaca</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>6293</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>71711</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="n">
+        <v>125223</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hortaleza</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>5431</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G47" s="18" t="n">
+        <v>61472</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="n">
+        <v>205182</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Barajas</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>5111</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F48" s="23" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>58405</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="n">
+        <v>49612</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fuencarral-El Pardo</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>62385</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J49" s="18" t="n">
+        <v>253898</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pozuelo de Alarcón</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>5134</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E50" s="20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F50" s="23" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G50" s="18" t="n">
+        <v>96290</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I50" s="20" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J50" s="18" t="n">
+        <v>89770</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Majadahonda</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>4925</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E51" s="20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F51" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G51" s="18" t="n">
+        <v>74987</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I51" s="20" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>73625</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>7655</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E52" s="20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F52" s="23" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G52" s="18" t="n">
+        <v>64787</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="n">
+        <v>119757</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Boadilla del Monte</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>4279</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" s="20" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F53" s="23" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>89455</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I53" s="20" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="J53" s="18" t="n">
+        <v>66349</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chamberí</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>8971</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E54" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F54" s="23" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G54" s="18" t="n">
+        <v>65174</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J54" s="18" t="n">
+        <v>141984</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>9988</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F55" s="23" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G55" s="18" t="n">
+        <v>69147</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="n">
+        <v>149778</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chamartín</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Distrito Madrid</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>8150</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E56" s="20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G56" s="18" t="n">
+        <v>79274</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J56" s="18" t="n">
+        <v>148111</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Álamo, El</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>2070</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="n">
+        <v>36817</v>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I57" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J57" s="18" t="n">
+        <v>10594</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Algete</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>2308</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="n">
+        <v>57767</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I58" s="20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J58" s="18" t="n">
+        <v>21144</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Alpedrete</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>2679</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="n">
+        <v>51116</v>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I59" s="20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J59" s="18" t="n">
+        <v>15686</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Becerril de la Sierra</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>2265</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="n">
+        <v>45765</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" s="20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J60" s="18" t="n">
+        <v>6737</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Camarma de Esteruelas</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>2198</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="n">
+        <v>43253</v>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I61" s="20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J61" s="18" t="n">
+        <v>8331</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Campo Real</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="n">
+        <v>38067</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I62" s="20" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J62" s="18" t="n">
+        <v>6974</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chinchón</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>1357</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="n">
+        <v>33815</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I63" s="20" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="J63" s="18" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ciempozuelos</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="n">
+        <v>40944</v>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" s="20" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J64" s="18" t="n">
+        <v>26350</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Collado Mediano</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>2284</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="n">
+        <v>50414</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I65" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J65" s="18" t="n">
+        <v>7722</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Colmenarejo</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>2415</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="n">
+        <v>49871</v>
+      </c>
+      <c r="H66" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I66" s="20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J66" s="18" t="n">
+        <v>9640</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Escorial, El</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>2639</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="n">
+        <v>45779</v>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I67" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" s="18" t="n">
+        <v>17171</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Griñón</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>2228</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="n">
+        <v>51037</v>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I68" s="20" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="J68" s="18" t="n">
+        <v>10799</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guadalix de la Sierra</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="n">
+        <v>41488</v>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I69" s="20" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J69" s="18" t="n">
+        <v>6993</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guadarrama</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>2680</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="n">
+        <v>44863</v>
+      </c>
+      <c r="H70" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I70" s="20" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J70" s="18" t="n">
+        <v>17547</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Humanes de Madrid</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>2544</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="n">
+        <v>36888</v>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I71" s="20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J71" s="18" t="n">
+        <v>20500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Loeches</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>2055</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="n">
+        <v>42908</v>
+      </c>
+      <c r="H72" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I72" s="20" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="J72" s="18" t="n">
+        <v>9261</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Manzanares el Real</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>2575</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="n">
+        <v>44742</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I73" s="20" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>9648</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Meco</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>2308</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="n">
+        <v>48565</v>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I74" s="20" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J74" s="18" t="n">
+        <v>15922</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Mejorada del Campo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>2417</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="n">
+        <v>38219</v>
+      </c>
+      <c r="H75" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I75" s="20" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="J75" s="18" t="n">
+        <v>25049</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Miraflores de la Sierra</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>2069</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="n">
+        <v>41298</v>
+      </c>
+      <c r="H76" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" s="20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J76" s="18" t="n">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Molar, El</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="n">
+        <v>37511</v>
+      </c>
+      <c r="H77" s="19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I77" s="20" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J77" s="18" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Moralzarzal</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
+        <v>2714</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="n">
+        <v>53552</v>
+      </c>
+      <c r="H78" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I78" s="20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J78" s="18" t="n">
+        <v>14772</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Pedrezuela</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>2522</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="n">
+        <v>42764</v>
+      </c>
+      <c r="H79" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I79" s="20" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="J79" s="18" t="n">
+        <v>6606</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Robledo de Chavela</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n">
+        <v>1759</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="n">
+        <v>37151</v>
+      </c>
+      <c r="H80" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I80" s="20" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J80" s="18" t="n">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>San Agustín del Guadalix</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>3046</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="n">
+        <v>60674</v>
+      </c>
+      <c r="H81" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J81" s="18" t="n">
+        <v>13825</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>San Fernando de Henares</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>2951</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="n">
+        <v>40448</v>
+      </c>
+      <c r="H82" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I82" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="J82" s="18" t="n">
+        <v>39059</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>San Martín de la Vega</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="n">
+        <v>38563</v>
+      </c>
+      <c r="H83" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I83" s="20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J83" s="18" t="n">
+        <v>21010</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>San Martín de Valdeiglesias</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="n">
+        <v>34141</v>
+      </c>
+      <c r="H84" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I84" s="20" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>9324</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Serranillos del Valle</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="n">
+        <v>48628</v>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J85" s="18" t="n">
+        <v>4670</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sevilla la Nueva</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>2605</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="n">
+        <v>45411</v>
+      </c>
+      <c r="H86" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I86" s="20" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J86" s="18" t="n">
+        <v>9802</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Torrejón de la Calzada</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>1965</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="n">
+        <v>47016</v>
+      </c>
+      <c r="H87" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J87" s="18" t="n">
+        <v>10653</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Tres Cantos</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>4047</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="n">
+        <v>67752</v>
+      </c>
+      <c r="H88" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I88" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="J88" s="18" t="n">
+        <v>54592</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Valdemorillo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>2462</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="n">
+        <v>48965</v>
+      </c>
+      <c r="H89" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I89" s="20" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>14420</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Velilla de San Antonio</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>2469</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="n">
+        <v>44913</v>
+      </c>
+      <c r="H90" s="19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I90" s="20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J90" s="18" t="n">
+        <v>14468</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Villalbilla</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G91" s="18" t="n">
+        <v>53793</v>
+      </c>
+      <c r="H91" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I91" s="20" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>18687</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Villanueva del Pardillo</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G92" s="18" t="n">
+        <v>59787</v>
+      </c>
+      <c r="H92" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>18466</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Villarejo de Salvanés</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>1416</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="n">
+        <v>34795</v>
+      </c>
+      <c r="H93" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I93" s="20" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="J93" s="18" t="n">
+        <v>8042</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>Barrios de Madrid con dato de alquiler y venta (rentabilidad bruta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="25" t="inlineStr">
+        <is>
+          <t>Barrio (oficial)</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>Zona idealista</t>
+        </is>
+      </c>
+      <c r="C97" s="25" t="inlineStr">
+        <is>
+          <t>Venta €/m²</t>
+        </is>
+      </c>
+      <c r="D97" s="25" t="inlineStr">
+        <is>
+          <t>Alquiler €/m²/mes</t>
+        </is>
+      </c>
+      <c r="E97" s="25" t="inlineStr">
+        <is>
+          <t>Rentab. bruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Numancia</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Numancia</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D98" s="19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E98" s="26" t="n">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="n">
+        <v>3487</v>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E99" s="26" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Pradolongo</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pradolongo</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D100" s="19" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E100" s="26" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Buena Vista</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n">
+        <v>3487</v>
+      </c>
+      <c r="D101" s="19" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E101" s="26" t="n">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Puerta Bonita</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Puerta Bonita</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="n">
+        <v>3534</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E102" s="26" t="n">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Palomeras Sureste</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Palomeras sureste</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n">
+        <v>3459</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E103" s="26" t="n">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>San Isidro</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>San Isidro</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n">
+        <v>3944</v>
+      </c>
+      <c r="D104" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E104" s="26" t="n">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Moscardó</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Moscardó</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n">
+        <v>3990</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E105" s="26" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Lucero</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Lucero</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D106" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="E106" s="26" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Puerta del Ángel</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Puerta del Ángel</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="n">
+        <v>4224</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E107" s="26" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Canillejas</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Canillejas</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n">
+        <v>4123</v>
+      </c>
+      <c r="D108" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E108" s="26" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n">
+        <v>4429</v>
+      </c>
+      <c r="D109" s="19" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E109" s="26" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Opañel</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Opañel</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="n">
+        <v>4028</v>
+      </c>
+      <c r="D110" s="19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E110" s="26" t="n">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Almenara</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ventilla-Almenara</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="n">
+        <v>5164</v>
+      </c>
+      <c r="D111" s="19" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E111" s="26" t="n">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Simancas</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Simancas</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n">
+        <v>4122</v>
+      </c>
+      <c r="D112" s="19" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E112" s="26" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Valverde</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tres Olivos - Valverde</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n">
+        <v>4371</v>
+      </c>
+      <c r="D113" s="19" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E113" s="26" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Bellas Vistas</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Bellas Vistas</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n">
+        <v>5486</v>
+      </c>
+      <c r="D114" s="19" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E114" s="26" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Aluche</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Aluche</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n">
+        <v>3913</v>
+      </c>
+      <c r="D115" s="19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E115" s="26" t="n">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Águilas</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Águilas</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D116" s="19" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E116" s="26" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Embajadores</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Lavapiés-Embajadores</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="n">
+        <v>6346</v>
+      </c>
+      <c r="D117" s="19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E117" s="26" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ensanche de Vallecas</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ensanche de Vallecas - La Gavia</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="n">
+        <v>4429</v>
+      </c>
+      <c r="D118" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E118" s="26" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Comillas</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Comillas</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="n">
+        <v>4652</v>
+      </c>
+      <c r="D119" s="19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E119" s="26" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Valdeacederas</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Valdeacederas</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="n">
+        <v>5303</v>
+      </c>
+      <c r="D120" s="19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E120" s="26" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Berruguete</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Berruguete</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="n">
+        <v>5368</v>
+      </c>
+      <c r="D121" s="19" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E121" s="26" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D122" s="19" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E122" s="26" t="n">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Quintana</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Quintana</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="n">
+        <v>5251</v>
+      </c>
+      <c r="D123" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E123" s="26" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Valdezarza</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Valdezarza</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="n">
+        <v>5096</v>
+      </c>
+      <c r="D124" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E124" s="26" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Pinar del Rey</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pinar del Rey</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="n">
+        <v>4982</v>
+      </c>
+      <c r="D125" s="19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E125" s="26" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>La Concepción</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="n">
+        <v>5364</v>
+      </c>
+      <c r="D126" s="19" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E126" s="26" t="n">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Pilar</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pilar</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="n">
+        <v>5536</v>
+      </c>
+      <c r="D127" s="19" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E127" s="26" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Peñagrande</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Peñagrande</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="n">
+        <v>5151</v>
+      </c>
+      <c r="D128" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E128" s="26" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Chopera</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Chopera</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="n">
+        <v>6037</v>
+      </c>
+      <c r="D129" s="19" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E129" s="26" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Palos de Moguer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Palos de Moguer</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="n">
+        <v>6304</v>
+      </c>
+      <c r="D130" s="19" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E130" s="26" t="n">
+        <v>4.44</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Delicias</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Delicias</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="n">
+        <v>6443</v>
+      </c>
+      <c r="D131" s="19" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E131" s="26" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>El Cañaveral</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>El Cañaveral - Los Berrocales</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="n">
+        <v>4449</v>
+      </c>
+      <c r="D132" s="19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E132" s="26" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Marroquina</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Marroquina</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="n">
+        <v>4891</v>
+      </c>
+      <c r="D133" s="19" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E133" s="26" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Rejas</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Rejas</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="n">
+        <v>4196</v>
+      </c>
+      <c r="D134" s="19" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E134" s="26" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="n">
+        <v>6460</v>
+      </c>
+      <c r="D135" s="19" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E135" s="26" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Universidad</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Malasaña-Universidad</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="n">
+        <v>7879</v>
+      </c>
+      <c r="D136" s="19" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E136" s="26" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Imperial</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Imperial</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="n">
+        <v>6429</v>
+      </c>
+      <c r="D137" s="19" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E137" s="26" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="n">
+        <v>5652</v>
+      </c>
+      <c r="D138" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E138" s="26" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Ciudad Universitaria</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ciudad Universitaria</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="n">
+        <v>6107</v>
+      </c>
+      <c r="D139" s="19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E139" s="26" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Canillas</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Canillas</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="n">
+        <v>5165</v>
+      </c>
+      <c r="D140" s="19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E140" s="26" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guindalera</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Guindalera</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="n">
+        <v>7268</v>
+      </c>
+      <c r="D141" s="19" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E141" s="26" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Palacio</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Palacio</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="n">
+        <v>7601</v>
+      </c>
+      <c r="D142" s="19" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E142" s="26" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Casa de Campo</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Casa de Campo</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="n">
+        <v>6208</v>
+      </c>
+      <c r="D143" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E143" s="26" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Cuatro Caminos</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Cuatro Caminos</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="n">
+        <v>7286</v>
+      </c>
+      <c r="D144" s="19" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E144" s="26" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Pacífico</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pacífico</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="n">
+        <v>6721</v>
+      </c>
+      <c r="D145" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E145" s="26" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>San Pascual</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>San Pascual</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="n">
+        <v>5998</v>
+      </c>
+      <c r="D146" s="19" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E146" s="26" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="n">
+        <v>7924</v>
+      </c>
+      <c r="D147" s="19" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E147" s="26" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Adelfas</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Adelfas</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="n">
+        <v>6343</v>
+      </c>
+      <c r="D148" s="19" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E148" s="26" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cortes</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Huertas-Cortes</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="n">
+        <v>8035</v>
+      </c>
+      <c r="D149" s="19" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E149" s="26" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Los Jerónimos</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Jerónimos</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="n">
+        <v>7980</v>
+      </c>
+      <c r="D150" s="19" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E150" s="26" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ciudad Jardín</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ciudad Jardín</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="n">
+        <v>7342</v>
+      </c>
+      <c r="D151" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E151" s="26" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Aravaca</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Aravaca</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="n">
+        <v>5444</v>
+      </c>
+      <c r="D152" s="19" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E152" s="26" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Estrella</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Estrella</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="n">
+        <v>6701</v>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E153" s="26" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="n">
+        <v>6676</v>
+      </c>
+      <c r="D154" s="19" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E154" s="26" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Castillejos</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Cuzco-Castillejos</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D155" s="19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E155" s="26" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Argüelles</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Argüelles</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="n">
+        <v>8180</v>
+      </c>
+      <c r="D156" s="19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E156" s="26" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Niño Jesús</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Niño Jesús</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="n">
+        <v>7568</v>
+      </c>
+      <c r="D157" s="19" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E157" s="26" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Chueca-Justicia</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="n">
+        <v>9471</v>
+      </c>
+      <c r="D158" s="19" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E158" s="26" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Fuente del Berro</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Fuente del Berro</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="n">
+        <v>7739</v>
+      </c>
+      <c r="D159" s="19" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E159" s="26" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Prosperidad</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Prosperidad</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="n">
+        <v>7502</v>
+      </c>
+      <c r="D160" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E160" s="26" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Legazpi</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Legazpi</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="n">
+        <v>6688</v>
+      </c>
+      <c r="D161" s="19" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E161" s="26" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Gaztambide</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Gaztambide</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="n">
+        <v>8264</v>
+      </c>
+      <c r="D162" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E162" s="26" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Costillares</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Costillares</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="n">
+        <v>6298</v>
+      </c>
+      <c r="D163" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="E163" s="26" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Alameda de Osuna</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Alameda de Osuna</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="n">
+        <v>5426</v>
+      </c>
+      <c r="D164" s="19" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="E164" s="26" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Trafalgar</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Trafalgar</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="n">
+        <v>9464</v>
+      </c>
+      <c r="D165" s="19" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E165" s="26" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Vallehermoso</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Vallehermoso</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="n">
+        <v>7952</v>
+      </c>
+      <c r="D166" s="19" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E166" s="26" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Palomas</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Palomas</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="n">
+        <v>5473</v>
+      </c>
+      <c r="D167" s="19" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="E167" s="26" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Ríos Rosas</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Nuevos Ministerios-Ríos Rosas</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="n">
+        <v>8835</v>
+      </c>
+      <c r="D168" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E168" s="26" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Arapiles</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Arapiles</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="n">
+        <v>8512</v>
+      </c>
+      <c r="D169" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E169" s="26" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Recoletos</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Recoletos</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="n">
+        <v>11111</v>
+      </c>
+      <c r="D170" s="19" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E170" s="26" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Castilla</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Castilla</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="n">
+        <v>7117</v>
+      </c>
+      <c r="D171" s="19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E171" s="26" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Valdefuentes</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Valdebebas - Valdefuentes</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="n">
+        <v>6080</v>
+      </c>
+      <c r="D172" s="19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E172" s="26" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>San Juan Bautista</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>San Juan Bautista</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="n">
+        <v>6883</v>
+      </c>
+      <c r="D173" s="19" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E173" s="26" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Mirasierra</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Mirasierra</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="n">
+        <v>6435</v>
+      </c>
+      <c r="D174" s="19" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E174" s="26" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Ibiza</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ibiza</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="n">
+        <v>9504</v>
+      </c>
+      <c r="D175" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="E175" s="26" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Goya</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Goya</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="n">
+        <v>10390</v>
+      </c>
+      <c r="D176" s="19" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E176" s="26" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Hispanoamérica</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Bernabéu-Hispanoamérica</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="n">
+        <v>8622</v>
+      </c>
+      <c r="D177" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E177" s="26" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Piovera</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Conde Orgaz-Piovera</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="n">
+        <v>6532</v>
+      </c>
+      <c r="D178" s="19" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E178" s="26" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="n">
+        <v>10582</v>
+      </c>
+      <c r="D179" s="19" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E179" s="26" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Castellana</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Castellana</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="n">
+        <v>11093</v>
+      </c>
+      <c r="D180" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E180" s="26" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Nueva España</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Nueva España</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="n">
+        <v>8706</v>
+      </c>
+      <c r="D181" s="19" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E181" s="26" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>El Viso</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>El Viso</t>
+        </is>
+      </c>
+      <c r="C182" s="18" t="n">
+        <v>9618</v>
+      </c>
+      <c r="D182" s="19" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E182" s="26" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Lista</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Lista</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="n">
+        <v>10612</v>
+      </c>
+      <c r="D183" s="19" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E183" s="26" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -6687,6 +12152,20 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Hoja "Rentabilidad y esfuerzo" (añadida jul-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rentabilidad bruta = alquiler×12/venta (idealista). Esfuerzo = venta×80m² / renta neta media hogar (INE 2023). Verde=cuartil superior de rentabilidad, rojo=inferior.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
